--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2701,8 +2817,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2713,674 +2833,736 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강강술래 — 민요채보-1/강강술래.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">강강술래</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="15"/>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">산아</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">잎이</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="E4" s="16"/>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="16"/>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="16"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="C5" s="16"/>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="16"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C6" s="17"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">손을</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">술</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">잡자</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 黃
 潢</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="G8" s="16"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="C9" s="16"/>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="E10" s="17"/>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">밤새</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">도록</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="C13" s="16"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">피</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">놀아</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">유</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" s="15"/>
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">보세</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E16" s="16"/>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢
 南</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="16"/>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">산아</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">화산</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="17"/>
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
+      <c r="I18" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">기호</t>
   </si>
   <si>
-    <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+    <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
   </si>
   <si>
     <t xml:space="preserve">노란 칸</t>
@@ -171,7 +171,7 @@
     <t xml:space="preserve">강</t>
   </si>
   <si>
-    <t xml:space="preserve">―</t>
+    <t xml:space="preserve">–</t>
   </si>
   <si>
     <t xml:space="preserve">姑|姑</t>
@@ -207,10 +207,10 @@
     <t xml:space="preserve">수</t>
   </si>
   <si>
-    <t xml:space="preserve">―|潢|南</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―
+    <t xml:space="preserve">–|潢|南</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
 潢
 南</t>
   </si>
@@ -265,10 +265,10 @@
     <t xml:space="preserve">화산</t>
   </si>
   <si>
-    <t xml:space="preserve">―|△</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―
+    <t xml:space="preserve">–|△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
 △</t>
   </si>
   <si>
@@ -304,10 +304,10 @@
     <t xml:space="preserve">손을</t>
   </si>
   <si>
-    <t xml:space="preserve">―|姑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―
+    <t xml:space="preserve">–|姑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
 姑</t>
   </si>
   <si>
@@ -366,7 +366,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌
-―
+–
 㴌㴌</t>
     </r>
   </si>
@@ -393,8 +393,8 @@
         <rFont val="맑은 고딕"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">―
-―</t>
+      <t xml:space="preserve">–
+–</t>
     </r>
   </si>
   <si>
@@ -418,7 +418,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">―
+      <t xml:space="preserve">–
 </t>
     </r>
     <r>
@@ -427,8 +427,8 @@
         <rFont val="맑은 고딕"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">―
-―</t>
+      <t xml:space="preserve">–
+–</t>
     </r>
   </si>
   <si>
@@ -457,12 +457,12 @@
         <rFont val="맑은 고딕"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">―</t>
+      <t xml:space="preserve">–</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">南南
-―
+–
 姑</t>
   </si>
   <si>
@@ -471,7 +471,7 @@
 잡</t>
   </si>
   <si>
-    <t xml:space="preserve">―
+    <t xml:space="preserve">–
 △
 㴌</t>
   </si>
@@ -482,7 +482,7 @@
   <si>
     <t xml:space="preserve">南
 南
-―</t>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">수
@@ -497,7 +497,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑
-―
+–
 </t>
     </r>
     <r>
@@ -620,13 +620,13 @@
   </si>
   <si>
     <t xml:space="preserve">南
-― 
+– 
 潢</t>
   </si>
   <si>
-    <t xml:space="preserve">―
-― 
-―</t>
+    <t xml:space="preserve">–
+– 
+–</t>
   </si>
   <si>
     <r>
@@ -711,7 +711,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑
-―</t>
+–</t>
     </r>
   </si>
   <si>
@@ -722,7 +722,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南
-―
+–
 </t>
     </r>
     <r>
@@ -751,7 +751,7 @@
   </si>
   <si>
     <t xml:space="preserve">南
-―
+–
 △ </t>
   </si>
 </sst>

--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -352,8 +352,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -361,8 +360,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌
@@ -379,8 +377,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -389,8 +386,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">–
@@ -413,8 +409,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -423,8 +418,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">–
@@ -434,8 +428,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南
@@ -443,8 +436,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -453,8 +445,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">–</t>
@@ -492,8 +483,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑
@@ -502,8 +492,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -517,8 +506,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -527,8 +515,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢㴌
@@ -543,8 +530,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -554,8 +540,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -568,8 +553,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南
@@ -578,8 +562,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -631,8 +614,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南
@@ -640,8 +622,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -649,8 +630,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南
@@ -670,8 +650,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -680,8 +659,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑南
@@ -696,8 +674,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -706,8 +683,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑
@@ -717,8 +693,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南
@@ -727,8 +702,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -762,56 +736,80 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="18"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -906,7 +904,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -956,6 +954,34 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3232,10 +3258,10 @@
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="22.05" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="7.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="7.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="7.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="7.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="7.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="7.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="7.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="7.07"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3244,214 +3270,214 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="16" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="18"/>
+      <c r="F4" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="18"/>
+      <c r="H4" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="18" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="18" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="19" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="16" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="18"/>
+      <c r="F8" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="8" t="s">
+      <c r="G8" s="18"/>
+      <c r="H8" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="18" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="18" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="19" t="s">
         <v>121</v>
       </c>
     </row>

--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -3258,9 +3258,13 @@
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="22.05" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.61"/>
+    <col min="2" max="2" width="14.14" customWidth="1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="7.07"/>
+    <col min="4" max="4" width="14.14" customWidth="1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="7.07"/>
+    <col min="6" max="6" width="14.14" customWidth="1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="7.07"/>
+    <col min="8" max="8" width="14.14" customWidth="1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="7.07"/>
   </cols>
   <sheetData>
@@ -3269,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
@@ -3281,7 +3285,7 @@
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
     </row>
-    <row r="3" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="15" t="s">
         <v>100</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
         <v>106</v>
       </c>
@@ -3329,7 +3333,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="s">
         <v>110</v>
       </c>
@@ -3355,7 +3359,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="15" t="s">
         <v>116</v>
       </c>
@@ -3381,7 +3385,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="15" t="s">
         <v>122</v>
       </c>
@@ -3407,7 +3411,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="15" t="s">
         <v>127</v>
       </c>
@@ -3429,7 +3433,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="15" t="s">
         <v>132</v>
       </c>
@@ -3455,7 +3459,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="104.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="15" t="s">
         <v>138</v>
       </c>
@@ -3481,6 +3485,14 @@
         <v>121</v>
       </c>
     </row>
+    <row r="11" ht="82.06" customHeight="true"/>
+    <row r="12" ht="82.06" customHeight="true"/>
+    <row r="13" ht="82.06" customHeight="true"/>
+    <row r="14" ht="82.06" customHeight="true"/>
+    <row r="15" ht="82.06" customHeight="true"/>
+    <row r="16" ht="82.06" customHeight="true"/>
+    <row r="17" ht="82.06" customHeight="true"/>
+    <row r="18" ht="82.06" customHeight="true"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>

--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="143">
   <si>
     <t xml:space="preserve">강강술래</t>
   </si>
@@ -727,6 +727,9 @@
     <t xml:space="preserve">南
 –
 △ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -1903,10 +1906,10 @@
         <v>4</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="3"/>

--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -907,7 +907,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -985,6 +985,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3262,13 +3278,13 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.61"/>
     <col min="2" max="2" width="14.14" customWidth="1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="7.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="7.07"/>
     <col min="4" max="4" width="14.14" customWidth="1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="7.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="7.07"/>
     <col min="6" max="6" width="14.14" customWidth="1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="7.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="20" width="7.07"/>
     <col min="8" max="8" width="14.14" customWidth="1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="7.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="7.07"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3292,25 +3308,25 @@
       <c r="B3" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="21" t="s">
         <v>101</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="21" t="s">
         <v>103</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="21" t="s">
         <v>103</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="21" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3318,21 +3334,21 @@
       <c r="B4" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="22" t="s">
         <v>107</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="18"/>
+      <c r="E4" s="22"/>
       <c r="F4" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="22" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3340,25 +3356,25 @@
       <c r="B5" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="22" t="s">
         <v>111</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="22" t="s">
         <v>113</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="22" t="s">
         <v>113</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="22" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3366,25 +3382,25 @@
       <c r="B6" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="23" t="s">
         <v>117</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="23" t="s">
         <v>119</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="23" t="s">
         <v>119</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="23" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3392,25 +3408,25 @@
       <c r="B7" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="21" t="s">
         <v>123</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="21" t="s">
         <v>125</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="21" t="s">
         <v>125</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="21" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3418,21 +3434,21 @@
       <c r="B8" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>128</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="18"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="18"/>
+      <c r="G8" s="22"/>
       <c r="H8" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="22" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3440,25 +3456,25 @@
       <c r="B9" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="22" t="s">
         <v>133</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="22" t="s">
         <v>135</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="22" t="s">
         <v>135</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="22" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3466,25 +3482,25 @@
       <c r="B10" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="23" t="s">
         <v>139</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="23" t="s">
         <v>140</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="23" t="s">
         <v>140</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="23" t="s">
         <v>121</v>
       </c>
     </row>

--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -831,10 +831,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -350,23 +350,9 @@
 어</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
+    <t xml:space="preserve">㴌㴌
 –
 㴌㴌</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">잎
@@ -375,23 +361,9 @@
 면</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">姑
+–
 –</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">강
@@ -407,49 +379,14 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">–
+–
 –</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">南
+姑
+–</t>
   </si>
   <si>
     <t xml:space="preserve">南南
@@ -481,46 +418,18 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑
+    <t xml:space="preserve">姑
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+△</t>
   </si>
   <si>
     <t xml:space="preserve">자
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">淋
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢㴌
+    <t xml:space="preserve">淋
+潢㴌
 △</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">산
@@ -528,46 +437,18 @@
 요</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">潢
 南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">래
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
 㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">밤
@@ -612,30 +493,9 @@
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
+姑南
 姑</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -648,23 +508,9 @@
 보</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑南
+    <t xml:space="preserve">潢
+姑南
 姑</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">화
@@ -672,42 +518,14 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑
+    <t xml:space="preserve">潢
+姑
 –</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
+  </si>
+  <si>
+    <t xml:space="preserve">南
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">南
@@ -3268,7 +3086,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I10"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="22.05" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3284,12 +3102,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="7.07"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true">
       <c r="B1" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="51.28" customHeight="true">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
@@ -3301,7 +3119,7 @@
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
     </row>
-    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B3" s="15" t="s">
         <v>100</v>
       </c>
@@ -3327,7 +3145,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B4" s="15" t="s">
         <v>106</v>
       </c>
@@ -3349,7 +3167,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B5" s="15" t="s">
         <v>110</v>
       </c>
@@ -3375,7 +3193,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B6" s="15" t="s">
         <v>116</v>
       </c>
@@ -3401,7 +3219,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B7" s="15" t="s">
         <v>122</v>
       </c>
@@ -3427,7 +3245,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B8" s="15" t="s">
         <v>127</v>
       </c>
@@ -3449,7 +3267,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B9" s="15" t="s">
         <v>132</v>
       </c>
@@ -3475,7 +3293,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B10" s="15" t="s">
         <v>138</v>
       </c>
@@ -3501,21 +3319,13 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" ht="82.06" customHeight="true"/>
-    <row r="12" ht="82.06" customHeight="true"/>
-    <row r="13" ht="82.06" customHeight="true"/>
-    <row r="14" ht="82.06" customHeight="true"/>
-    <row r="15" ht="82.06" customHeight="true"/>
-    <row r="16" ht="82.06" customHeight="true"/>
-    <row r="17" ht="82.06" customHeight="true"/>
-    <row r="18" ht="82.06" customHeight="true"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="78"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/강강술래.xlsx
+++ b/sheets/민요/검수/강강술래.xlsx
@@ -3092,13 +3092,13 @@
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="22.05" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.61"/>
-    <col min="2" max="2" width="14.14" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="7.07"/>
-    <col min="4" max="4" width="14.14" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="7.07"/>
-    <col min="6" max="6" width="14.14" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="20" width="7.07"/>
-    <col min="8" max="8" width="14.14" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="7.07"/>
   </cols>
   <sheetData>
